--- a/output/full_scan/batch_seq5_2026-06-11.xlsx
+++ b/output/full_scan/batch_seq5_2026-06-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O151"/>
+  <dimension ref="A1:O153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5356</v>
+        <v>6126</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>協益</t>
+          <t>信音</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>853.820425538829</v>
+        <v>1161.254243555169</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>28.3</v>
+        <v>41.55</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.4530252435238</v>
+        <v>61.9763507207981</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27.43454008433267</v>
+        <v>29.19779615289449</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.8820425538829</v>
+        <v>2.125424355516884</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0876707852293893</v>
+        <v>0.228723196721277</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5468</v>
+        <v>4904</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>凱鈺</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>821.7883316651134</v>
+        <v>1090.321191521747</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.8</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.1492553016538</v>
+        <v>78.12292250142181</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12.91745425582461</v>
+        <v>30.53920557467267</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.17883316651135</v>
+        <v>1.032119152174688</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1457993070354339</v>
+        <v>1.233097590355707</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5285</v>
+        <v>6121</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>界霖</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>794.0752201135132</v>
+        <v>1024.870012106321</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>86.8</v>
+        <v>411</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.15418543597567</v>
+        <v>60.37944100342057</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>51.46710075819559</v>
+        <v>30.78180269061293</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4075220113513162</v>
+        <v>0.9870012106321336</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-1.417730146066803</v>
+        <v>0.4957188885808392</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4958</v>
+        <v>5356</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>協益</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>790.2897637543931</v>
+        <v>1023.820425538829</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>529</v>
+        <v>28.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.88198964174332</v>
+        <v>70.45302516459373</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.30145705942763</v>
+        <v>27.43453955353321</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.52897637543931</v>
+        <v>1.8820425538829</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-5.489191621864201</v>
+        <v>0.0876707853724842</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6121</v>
+        <v>5468</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>凱鈺</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>764.8700121063214</v>
+        <v>1021.788331665113</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>411</v>
+        <v>19.8</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.37944108412755</v>
+        <v>68.14925516200331</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30.78180268553145</v>
+        <v>12.91745403843326</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9870012106321336</v>
+        <v>4.17883316651135</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4957188881992849</v>
+        <v>0.1457993070926705</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4919</v>
+        <v>5285</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>界霖</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>755.7503721676801</v>
+        <v>999.1075327207184</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>172.5</v>
+        <v>86.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>49.27070946553577</v>
+        <v>59.15418543022442</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.64922407839378</v>
+        <v>51.46710074266814</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.575037216768013</v>
+        <v>0.4107532720718441</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-6.066749228135196</v>
+        <v>-1.417730146114507</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5425</v>
+        <v>4958</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>735.3678634870704</v>
+        <v>990.6263038105</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>529</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>52.03671557436773</v>
+        <v>59.88198963590393</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.18836555470579</v>
+        <v>33.30145706419651</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5367863487070436</v>
+        <v>1.562630381050002</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-2.675129288094146</v>
+        <v>-5.489191621539845</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5227</v>
+        <v>4938</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>立凱-KY</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>724.6626109620469</v>
+        <v>926.2130519180912</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>28.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.93312815600501</v>
+        <v>66.74799564715832</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.02156412147512</v>
+        <v>30.92058596131612</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.966261096204683</v>
+        <v>1.121305191809129</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.197237448021068</v>
+        <v>0.7101202594593419</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5381</v>
+        <v>5227</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>光譜</t>
+          <t>立凱-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>723.9004090565647</v>
+        <v>924.6626109620468</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.65</v>
+        <v>28.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.59006277655338</v>
+        <v>65.93312811278258</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>37.92904723185128</v>
+        <v>21.02156415415568</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.39004090565647</v>
+        <v>1.966261096204683</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5946876919545301</v>
+        <v>0.1972374479542903</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4916</v>
+        <v>6113</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>事欣科</t>
+          <t>亞矽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>721.9650779586499</v>
+        <v>910.0428769632508</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>114.5</v>
+        <v>27.15</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.39423329824342</v>
+        <v>58.9673682190249</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46.76772746324765</v>
+        <v>28.16200350807285</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.196507795864987</v>
+        <v>2.004287696325097</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.5326097389557312</v>
+        <v>-0.1927870490634243</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5299</v>
+        <v>5536</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>杰力</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>712.7529616099603</v>
+        <v>909.9227812169368</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>100.5</v>
+        <v>1075</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45.57886170784757</v>
+        <v>57.86524799655054</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.47062279726487</v>
+        <v>30.88603107491669</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.2752961609960262</v>
+        <v>0.4922781216936754</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-2.638062895067478</v>
+        <v>0.4397125369934045</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4952</v>
+        <v>6155</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>凌通</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>705.6579212423381</v>
+        <v>904.4346205351573</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>51.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53.98985528540032</v>
+        <v>71.37632750216321</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.46444684768957</v>
+        <v>42.53371542759299</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.065792124233812</v>
+        <v>1.443462053515726</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.6078676564809437</v>
+        <v>1.415413664169746</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4904</v>
+        <v>5381</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>光譜</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>705.220494929339</v>
+        <v>893.9004090565647</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>109</v>
+        <v>30.65</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>78.12292246772394</v>
+        <v>59.59006273418554</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.53920551640945</v>
+        <v>37.92904732881857</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.022049492933904</v>
+        <v>1.39004090565647</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.233097590489251</v>
+        <v>0.5946876919091131</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5536</v>
+        <v>5228</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>699.9227812169368</v>
+        <v>887.0806046577231</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1075</v>
+        <v>71.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.86524801975207</v>
+        <v>74.02705299382595</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.88603111056188</v>
+        <v>48.73340894192335</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4922781216936754</v>
+        <v>1.708060465772315</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4397125337496774</v>
+        <v>0.4361976675932535</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5228</v>
+        <v>5328</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>華容</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>687.0806046577231</v>
+        <v>875.7536988278362</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>71.5</v>
+        <v>43.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>74.02705233947924</v>
+        <v>68.93022114007549</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>48.73340762313667</v>
+        <v>33.30998921682445</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.708060465772315</v>
+        <v>2.075369882783615</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.4361976704933266</v>
+        <v>0.4684277942160113</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6155</v>
+        <v>4952</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>凌通</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>684.378607959309</v>
+        <v>875.7432999576873</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>71.37632750833535</v>
+        <v>53.98985521783648</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>42.53371539949674</v>
+        <v>23.46444682015769</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.437860795930897</v>
+        <v>1.074329995768738</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.415413664179287</v>
+        <v>-0.6078676564141665</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5328</v>
+        <v>5345</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>華容</t>
+          <t>天揚</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>675.7536988278362</v>
+        <v>865</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>43.2</v>
+        <v>35.35</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.93022115763924</v>
+        <v>65.72476465065262</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.30998921669418</v>
+        <v>9.453160217618493</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.075369882783615</v>
+        <v>6.70873657946469</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.4684277941969368</v>
+        <v>1.516787398917904</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6113</v>
+        <v>5471</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>亞矽</t>
+          <t>松翰</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>665.0428769632509</v>
+        <v>841.0483760560221</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>27.15</v>
+        <v>51.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.96736827836758</v>
+        <v>54.32223449513655</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.16200356046478</v>
+        <v>30.06491163229752</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.004287696325097</v>
+        <v>1.104837605602206</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.1927870494545538</v>
+        <v>-0.7428295428214908</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5345</v>
+        <v>5474</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天揚</t>
+          <t>聰泰</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>665</v>
+        <v>832.0314554573213</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.35</v>
+        <v>176.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>65.72476465008097</v>
+        <v>55.32063644802736</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9.453160237023511</v>
+        <v>30.71728556504618</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6.70873657946469</v>
+        <v>0.7031455457321302</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.516787398917904</v>
+        <v>-1.137496729114407</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5474</v>
+        <v>5434</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>聰泰</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>662.0314554573213</v>
+        <v>819.3871080357566</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>176.5</v>
+        <v>453</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.32063653783347</v>
+        <v>54.91226427781065</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.71728557494073</v>
+        <v>24.58713146193979</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7031455457321302</v>
+        <v>0.9387108035756616</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.137496729209785</v>
+        <v>-2.831448819828729</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5353</v>
+        <v>4939</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台林</t>
+          <t>亞電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>657.3014383279365</v>
+        <v>805.3593961629691</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>32.85</v>
+        <v>60.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.83842125120586</v>
+        <v>69.3852720947706</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>61.0600112912268</v>
+        <v>34.83986030316736</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7301438327936469</v>
+        <v>1.035939616296911</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3710563656984977</v>
+        <v>1.337231124024942</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4931</v>
+        <v>5353</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>台林</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>656.428116301468</v>
+        <v>797.3014383279365</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>234</v>
+        <v>32.85</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.77762461228825</v>
+        <v>65.83842114363769</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>40.58973935981951</v>
+        <v>61.06001128286825</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6428116301468013</v>
+        <v>0.7301438327936469</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3329645205468168</v>
+        <v>0.3710563656412562</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5274</v>
+        <v>5464</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>霖宏</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>654.5120172012195</v>
+        <v>782.3321682943442</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>17600</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.90838438605199</v>
+        <v>57.69130405250999</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.40306174122869</v>
+        <v>49.83647707667576</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9512017201219516</v>
+        <v>0.7332168294344191</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-196.174623877966</v>
+        <v>-1.929783984532533</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5484</v>
+        <v>5347</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>653.5148219697876</v>
+        <v>777.6810948289838</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>49.7</v>
+        <v>161.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.05120150279543</v>
+        <v>50.77949281130198</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45.64430352823554</v>
+        <v>16.17626988119437</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3514821969787555</v>
+        <v>0.7681094828983727</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,51 +1789,51 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.2292190278982686</v>
+        <v>-2.252860096749199</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4987</v>
+        <v>5274</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>科誠</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>647.5086491134235</v>
+        <v>769.5120172012195</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>17600</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.06266453445506</v>
+        <v>52.908384380418</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23.90739717104425</v>
+        <v>26.40306171992086</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.750864911342356</v>
+        <v>0.9512017201219516</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0408812904567149</v>
+        <v>-196.1746238817861</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4967</v>
+        <v>5484</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>643.4311512008964</v>
+        <v>753.5994326902463</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>277.5</v>
+        <v>49.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.50718896253071</v>
+        <v>53.05120146101572</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.72445392851441</v>
+        <v>45.64430354081271</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8431151200896331</v>
+        <v>0.3599432690246339</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.963834596076181</v>
+        <v>-0.2292190279936621</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5309</v>
+        <v>5493</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>三聯</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>639.6617207112556</v>
+        <v>743.3173175381639</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>44.80904455840544</v>
+        <v>50.88923769477752</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.78789934894426</v>
+        <v>27.90850552179418</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4661720711255656</v>
+        <v>1.331731753816392</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.8522042315974434</v>
+        <v>0.2497658019775039</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4938</v>
+        <v>4919</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>636.1617285000677</v>
+        <v>740.9434484276613</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>95.40000000000001</v>
+        <v>172.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>66.74799567019653</v>
+        <v>49.27070945476987</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.92058593015138</v>
+        <v>22.64922407920784</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.116172850006778</v>
+        <v>1.594344842766138</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7101202593830198</v>
+        <v>-6.066749228192444</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6141</v>
+        <v>6153</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>柏承</t>
+          <t>嘉聯益</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>629.714056337801</v>
+        <v>739.9147074881812</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>31.6</v>
+        <v>20.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>42.36649435025805</v>
+        <v>60.3011395381042</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.75160040571277</v>
+        <v>18.36080973557842</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4714056337801037</v>
+        <v>1.491470748818121</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-1.190360331077775</v>
+        <v>0.2172025744526329</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4939</v>
+        <v>5425</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>亞電</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>605.3593961629691</v>
+        <v>735.3678634870704</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>60.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>69.38527210542165</v>
+        <v>52.0367155640403</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34.8398603241396</v>
+        <v>36.1883655566018</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.035939616296911</v>
+        <v>0.5367863487070436</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.337231123948624</v>
+        <v>-2.675129288084614</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4545</v>
+        <v>5309</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>銘鈺</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>600.2706076488944</v>
+        <v>734.6617207112556</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>34.55</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>46.7425300715939</v>
+        <v>44.80904452712095</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>42.2742705201273</v>
+        <v>25.78789937204943</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.027060764889435</v>
+        <v>0.4661720711255656</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.3419995882340059</v>
+        <v>-0.8522042316260694</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5488</v>
+        <v>5450</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>松普</t>
+          <t>寶聯通</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>593.8482232053426</v>
+        <v>724.869046759476</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12</v>
+        <v>14.35</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.08100043585203</v>
+        <v>66.10696288525392</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>35.75991535747104</v>
+        <v>27.27580178300522</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3848223205342621</v>
+        <v>0.9869046759476</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.107214008386532</v>
+        <v>0.2168138278017832</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>4542</v>
+        <v>5388</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>科嶠</t>
+          <t>中磊</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>585.2633799147122</v>
+        <v>723.0478922368028</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>305</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.41862178834276</v>
+        <v>52.42020386207659</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>42.01085805618627</v>
+        <v>18.40773361202633</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.026337991471222</v>
+        <v>0.8047892236802759</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>4.668695946770502</v>
+        <v>-0.3908004871323349</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5464</v>
+        <v>5299</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>霖宏</t>
+          <t>杰力</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>582.3321682943442</v>
+        <v>712.7529616099603</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>100.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.69130405250999</v>
+        <v>45.57886165753963</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>49.83647711866526</v>
+        <v>41.47062281731757</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7332168294344191</v>
+        <v>0.2752961609960262</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.929783984503912</v>
+        <v>-2.638062894953001</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>4989</v>
+        <v>5490</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>同亨</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>581.9633007039367</v>
+        <v>712.5932555138642</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>28.25</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>34.84139674105093</v>
+        <v>46.873199364846</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.0943190634326</v>
+        <v>28.56241649198999</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6963300703936691</v>
+        <v>0.7593255513864194</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.622118654066291</v>
+        <v>-0.1707884749501989</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5289</v>
+        <v>5302</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>太欣</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>576.6159647651887</v>
+        <v>710.8378338858391</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1710</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.42415988654965</v>
+        <v>52.05548279569852</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>31.13929899405223</v>
+        <v>17.65684548196818</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.161596476518864</v>
+        <v>0.583783388583916</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-25.69793271979663</v>
+        <v>0.0563898988797463</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5269</v>
+        <v>4916</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>事欣科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>575.7556291721039</v>
+        <v>707.0581940587767</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1330</v>
+        <v>114.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>41.84026350074534</v>
+        <v>64.39423325913418</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.76244904572956</v>
+        <v>46.76772744316403</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5755629172103939</v>
+        <v>1.205819405877678</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-28.48052482778414</v>
+        <v>-0.5326097386599962</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5493</v>
+        <v>6112</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三聯</t>
+          <t>邁達特</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>573.3173175381639</v>
+        <v>704.7759391844329</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>46.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.88923775563529</v>
+        <v>52.17245475079319</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.90850555943591</v>
+        <v>22.86658863958038</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.331731753816392</v>
+        <v>0.4775939184432899</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2497658018248714</v>
+        <v>0.4090320563610806</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5471</v>
+        <v>4961</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>松翰</t>
+          <t>天鈺</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>570.9697184009899</v>
+        <v>694.9664449950243</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51.7</v>
+        <v>163</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.32223452870791</v>
+        <v>45.81704335123472</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>30.06491161849456</v>
+        <v>23.15512264661508</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.096971840098985</v>
+        <v>0.4966444995024322</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.7428295428024145</v>
+        <v>-1.755847801477046</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5386</v>
+        <v>6115</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>青雲</t>
+          <t>鎰勝</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>569.8595182445769</v>
+        <v>684.4145952002192</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>483</v>
+        <v>48.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.49950318971917</v>
+        <v>55.43917230809219</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.80819951529289</v>
+        <v>16.63453360050637</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9859518244576848</v>
+        <v>0.941459520021922</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-12.25242044858214</v>
+        <v>0.099688577655831</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>4906</v>
+        <v>5498</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>正文</t>
+          <t>凱崴</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>569.715689503582</v>
+        <v>672.1423914457487</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>42</v>
+        <v>66.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.02920855468733</v>
+        <v>51.68018677769027</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>31.27706648118615</v>
+        <v>13.76031211996544</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4715689503581966</v>
+        <v>1.714239144574865</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.8975646988432531</v>
+        <v>-0.157808535746744</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4760</v>
+        <v>6123</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>上奇</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>567.7290812746795</v>
+        <v>670.8383289970607</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>364.5</v>
+        <v>46.15</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.9072133855063</v>
+        <v>59.17920719638088</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.81098906271874</v>
+        <v>23.21244831781615</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7729081274679543</v>
+        <v>1.083832899706069</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-8.023364596723127</v>
+        <v>0.1426149485893147</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6112</v>
+        <v>4931</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>邁達特</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>564.69331897498</v>
+        <v>656.428116301468</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46.6</v>
+        <v>234</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.17245483231702</v>
+        <v>54.77762458891582</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.86658864667498</v>
+        <v>40.58973934591864</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4693318974980059</v>
+        <v>0.6428116301468013</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,48 +2796,48 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.4090320563515403</v>
+        <v>0.3329645206612994</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>5388</v>
+        <v>4987</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>中磊</t>
+          <t>科誠</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>562.9863731881865</v>
+        <v>647.5086491134235</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.42020386727631</v>
+        <v>55.06266248350222</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.40773356914256</v>
+        <v>23.90739703685718</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7986373188186542</v>
+        <v>0.750864911342356</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3908004871132491</v>
+        <v>-0.0408812903913472</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6139</v>
+        <v>4976</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>552.4014385636946</v>
+        <v>645.5971708418783</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>732</v>
+        <v>32.85</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.8627688688774</v>
+        <v>53.02535447649656</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.38396070419586</v>
+        <v>33.97577213661527</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7401438563694591</v>
+        <v>1.059717084187831</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-10.63860974458782</v>
+        <v>0.0527771119526772</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>4976</v>
+        <v>4995</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>佳凌</t>
+          <t>晶達</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>550.5563878841239</v>
+        <v>633.4638647374034</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>32.85</v>
+        <v>44.75</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.02535450254998</v>
+        <v>48.11597385230445</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>33.97577214878374</v>
+        <v>26.65735363782633</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.055638788412387</v>
+        <v>0.8463864737403382</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0527771119717611</v>
+        <v>-0.2946842966003526</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>5347</v>
+        <v>4924</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>欣厚-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>547.6810948289838</v>
+        <v>632.3395923214988</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>161.5</v>
+        <v>11.95</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.77949282936085</v>
+        <v>52.79246973571394</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.17626989511562</v>
+        <v>27.89833155853374</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7681094828983727</v>
+        <v>0.2339592321498806</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-2.252860096882736</v>
+        <v>-0.0802619283838355</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6115</v>
+        <v>6141</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>鎰勝</t>
+          <t>柏承</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>541.2580341524992</v>
+        <v>629.7530218053121</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>48.4</v>
+        <v>31.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.43917240091174</v>
+        <v>42.36649434286457</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.63453353645143</v>
+        <v>22.7516004316314</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6258034152499307</v>
+        <v>0.4753021805312106</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0996885776176699</v>
+        <v>-1.190360331085408</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6123</v>
+        <v>4967</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>上奇</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>530.8383289970607</v>
+        <v>628.5423212667386</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46.15</v>
+        <v>277.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>59.17920751728212</v>
+        <v>50.50718895003096</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.21244824618994</v>
+        <v>25.7244539575612</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.083832899706069</v>
+        <v>0.8542321266738561</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1426149484939194</v>
+        <v>-1.963834595980761</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5483</v>
+        <v>4915</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>529.0425547721469</v>
+        <v>619.2946647917432</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>145</v>
+        <v>75.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.10793960083406</v>
+        <v>53.04724474143612</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.24243419508655</v>
+        <v>14.62749830835051</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4042554772146876</v>
+        <v>0.929466479174318</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.854304035802667</v>
+        <v>0.1813819511819756</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>5450</v>
+        <v>4989</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>寶聯通</t>
+          <t>榮科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>524.8690467594761</v>
+        <v>602.0520538568064</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>14.35</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>66.10696289932443</v>
+        <v>34.84139673518729</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.27580178300522</v>
+        <v>25.09431903957471</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9869046759476</v>
+        <v>0.7052053856806489</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2168138278494819</v>
+        <v>-2.622118654047209</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4924</v>
+        <v>5278</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>欣厚-KY</t>
+          <t>尚凡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>517.3395923214988</v>
+        <v>598.6270914349769</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>11.95</v>
+        <v>24.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.79246977797681</v>
+        <v>56.56075514428344</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>27.89833156586408</v>
+        <v>12.3599789407276</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2339592321498806</v>
+        <v>1.362709143497696</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0802619283933752</v>
+        <v>0.137638160554659</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5243</v>
+        <v>5488</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>松普</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>509.827274778316</v>
+        <v>593.8482232053426</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>109.5</v>
+        <v>12</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.09702608777092</v>
+        <v>51.08100034734696</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.38740876332134</v>
+        <v>35.75991529916099</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4827274778315954</v>
+        <v>0.3848223205342621</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-2.131581791253072</v>
+        <v>-0.1072140082968587</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5490</v>
+        <v>4542</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>同亨</t>
+          <t>科嶠</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>507.5932555138642</v>
+        <v>585.2633799147122</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>28.25</v>
+        <v>305</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.87319943986676</v>
+        <v>61.41862178834276</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.56241643111644</v>
+        <v>42.01085805618627</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7593255513864194</v>
+        <v>2.026337991471222</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1707884749692793</v>
+        <v>4.668695946770502</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>5245</v>
+        <v>4966</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>智晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>504.7382522132724</v>
+        <v>585.1101755437667</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26</v>
+        <v>657</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.92309013539006</v>
+        <v>40.5767675815566</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>33.20128664670417</v>
+        <v>27.81669482116001</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9738252213272384</v>
+        <v>0.511017554376666</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,84 +3432,84 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1785439385378796</v>
+        <v>-27.90538042474493</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4945</v>
+        <v>5351</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陞達科技</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>499.2651276632713</v>
+        <v>584.440810172811</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.11392605322222</v>
+        <v>52.27989344279735</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12.9245221601512</v>
+        <v>19.30433576151317</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4265127663271301</v>
+        <v>0.9440810172810959</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.5438837737986613</v>
+        <v>-0.5798883333440719</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4966</v>
+        <v>5481</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>新華</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>495.1101755437667</v>
+        <v>578.3518432492674</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>657</v>
+        <v>19.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.57676758718201</v>
+        <v>49.02938833244156</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.81669481883259</v>
+        <v>21.39640726054373</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.511017554376666</v>
+        <v>0.8351843249267416</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-27.90538042379102</v>
+        <v>0.1678501325863621</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4991</v>
+        <v>5289</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>494.8320335310594</v>
+        <v>576.6159647651887</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>530</v>
+        <v>1710</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>35.90449968620487</v>
+        <v>50.42415987899509</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.62788274476172</v>
+        <v>31.1392989064198</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.983203353105944</v>
+        <v>1.161596476518864</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-30.81723640596458</v>
+        <v>-25.69793271855637</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4995</v>
+        <v>5269</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>晶達</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>493.4638647374034</v>
+        <v>576.3563996847133</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>44.75</v>
+        <v>1330</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.11597394982454</v>
+        <v>41.84026346559482</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.65735363701627</v>
+        <v>24.7624490762859</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8463864737403382</v>
+        <v>0.6356399684713321</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.2946842966385118</v>
+        <v>-28.48052483160004</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>5434</v>
+        <v>5386</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>青雲</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>484.2357573204287</v>
+        <v>569.8595182445769</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.91226433998403</v>
+        <v>48.49950318409237</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.58713149109442</v>
+        <v>25.80819950098536</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9235757320428714</v>
+        <v>0.9859518244576848</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.831448820019494</v>
+        <v>-12.25242044850584</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>5302</v>
+        <v>4906</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>太欣</t>
+          <t>正文</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>480.8378338858391</v>
+        <v>569.7492700181919</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.05548284995467</v>
+        <v>47.02920855338684</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.65684543004166</v>
+        <v>31.27706647408415</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.583783388583916</v>
+        <v>0.4749270018191832</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0563898988587599</v>
+        <v>-0.8975646989004917</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6153</v>
+        <v>4760</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>嘉聯益</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>479.8783356882111</v>
+        <v>567.7290812746795</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>20.3</v>
+        <v>364.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>60.30113955424973</v>
+        <v>51.9072133722547</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.36080971069688</v>
+        <v>31.81098902399217</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.487833568821105</v>
+        <v>0.7729081274679543</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2172025744717116</v>
+        <v>-8.023364596341573</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>5498</v>
+        <v>5355</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>凱崴</t>
+          <t>佳總</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>472.1423914457487</v>
+        <v>559.9020294849793</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>66.7</v>
+        <v>6.69</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.68018678308602</v>
+        <v>51.63980316637794</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.76031209705814</v>
+        <v>14.28017491104639</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.714239144574865</v>
+        <v>0.4902029484979328</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1578085357677285</v>
+        <v>0.0337776248198583</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>5351</v>
+        <v>5205</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>鈺創</t>
+          <t>中茂</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>469.440810172811</v>
+        <v>548.825264344136</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>84.3</v>
+        <v>23.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.2798934661442</v>
+        <v>52.76641630188055</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.30433578859887</v>
+        <v>21.53275054992324</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9440810172810959</v>
+        <v>0.8825264344136007</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.5798883333440719</v>
+        <v>0.1649364076325444</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>4961</v>
+        <v>5230</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>天鈺</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>439.8610781386819</v>
+        <v>542.5115394963243</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>163</v>
+        <v>17.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45.81704345069775</v>
+        <v>52.49500803944773</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.15512251863712</v>
+        <v>16.33406454058587</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4861078138681876</v>
+        <v>0.7511539496324371</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.755847801477046</v>
+        <v>0.0251745180870036</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>5251</v>
+        <v>4545</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>天鉞電</t>
+          <t>銘鈺</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>438.1189228297058</v>
+        <v>540.3108731399025</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>30</v>
+        <v>34.55</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.02096172396586</v>
+        <v>46.7425300448392</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>32.61791354922757</v>
+        <v>42.27427053759622</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3118922829705813</v>
+        <v>1.031087313990241</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2283779394002738</v>
+        <v>-0.3419995882626203</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>4577</v>
+        <v>4912</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>達航科技</t>
+          <t>聯德控股-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>437.7363137210006</v>
+        <v>538.3311280612454</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>28.30071003805243</v>
+        <v>42.69965455263806</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>29.88206698639902</v>
+        <v>26.14511023432163</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7736313721000595</v>
+        <v>0.3331128061245424</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.954973521186849</v>
+        <v>-2.322730316795849</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>4912</v>
+        <v>6139</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>聯德控股-KY</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>423.2833667485666</v>
+        <v>537.6649725443625</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>732</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.699654601345</v>
+        <v>47.86276887702904</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.14511023632808</v>
+        <v>23.38396069937244</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3283366748566609</v>
+        <v>0.7664972544362521</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-2.322730316834008</v>
+        <v>-10.6386097451604</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>5355</v>
+        <v>5291</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>佳總</t>
+          <t>邑昇</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>419.9020294849793</v>
+        <v>533.8618514521877</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>6.69</v>
+        <v>64.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.63980326597636</v>
+        <v>41.48115252553193</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.28017488062566</v>
+        <v>19.05778949563517</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4902029484979328</v>
+        <v>0.3861851452187674</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0337776248198583</v>
+        <v>-1.041275753034755</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>5481</v>
+        <v>4923</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>新華</t>
+          <t>力士</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>408.3518432492674</v>
+        <v>532.7999002157703</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>19.5</v>
+        <v>43.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.0294591607945</v>
+        <v>53.01233478937493</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.39639269707581</v>
+        <v>18.56861143006579</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8351843249267416</v>
+        <v>0.279990021577026</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.167850009127453</v>
+        <v>-0.3539608306641764</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>4956</v>
+        <v>5483</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>光鋐</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>404.3901366876969</v>
+        <v>529.0425547721469</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>37.3</v>
+        <v>145</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>35.13087151616035</v>
+        <v>47.10793959194007</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.88679819468961</v>
+        <v>23.24243419096181</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4390136687696893</v>
+        <v>0.4042554772146876</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.110429042815326</v>
+        <v>-2.854304035898057</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>4915</v>
+        <v>4943</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>康控-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>404.2619862018735</v>
+        <v>526.3897157567135</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>75.2</v>
+        <v>8.99</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.04724471237582</v>
+        <v>45.70012552304998</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.62749825733214</v>
+        <v>16.66204613039691</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9261986201873532</v>
+        <v>1.638971575671357</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1813819514490793</v>
+        <v>0.0560435469513125</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>4729</v>
+        <v>5348</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>熒茂</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>403.2005606842843</v>
+        <v>520.61382301703</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>21.1</v>
+        <v>16.45</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.75969934778345</v>
+        <v>53.65872910932388</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38.89966855632253</v>
+        <v>13.59667928966532</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3200560684284319</v>
+        <v>0.5613823017029901</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.5620633119874964</v>
+        <v>0.3909080994428157</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>5230</v>
+        <v>5243</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>402.5115394963244</v>
+        <v>519.8778199366777</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>17.6</v>
+        <v>109.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>52.49500814164471</v>
+        <v>46.09702607817528</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.33406453098848</v>
+        <v>20.38740877700507</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7511539496324371</v>
+        <v>0.4877819936677731</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0251745180583869</v>
+        <v>-2.13158179130077</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>4949</v>
+        <v>5489</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>有成精密</t>
+          <t>彩富</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>399.6581968905512</v>
+        <v>518.4754473684059</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>90</v>
+        <v>39.45</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.25568787402306</v>
+        <v>46.4447357496606</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23.57290957512389</v>
+        <v>32.73673591192279</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4658196890551177</v>
+        <v>0.3475447368405854</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.548229952292448</v>
+        <v>0.0525801618008576</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>4951</v>
+        <v>4577</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>精拓科</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>398.7698041159516</v>
+        <v>512.7363137210007</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.15632891783849</v>
+        <v>28.30071002794938</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>32.66355326740381</v>
+        <v>29.88206698639902</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8769804115951607</v>
+        <v>0.7736313721000595</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-4.516781093748968</v>
+        <v>-2.954973521120076</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>5215</v>
+        <v>6104</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>科嘉-KY</t>
+          <t>創惟</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>395.9936420103706</v>
+        <v>510.533185890469</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>42.15</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.53030432249624</v>
+        <v>47.7043851251668</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>44.85194138111687</v>
+        <v>21.07293695630297</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.099364201037067</v>
+        <v>1.053318589046899</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.9070166235812472</v>
+        <v>-0.2952471224655838</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6104</v>
+        <v>5245</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>創惟</t>
+          <t>智晶</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>395.533185890469</v>
+        <v>504.7382522132724</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.70438531952225</v>
+        <v>46.92309005788987</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.07293685122772</v>
+        <v>33.20128662538487</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.053318589046899</v>
+        <v>0.9738252213272384</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2952471221793957</v>
+        <v>-0.1785439385283411</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>4923</v>
+        <v>5258</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>力士</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>392.7999002157703</v>
+        <v>500.9944793398264</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>43.2</v>
+        <v>50.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.01233479810941</v>
+        <v>46.74638932541153</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.56861146041398</v>
+        <v>20.50702597274747</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.279990021577026</v>
+        <v>0.5994479339826422</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,51 +4704,51 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3539608307786581</v>
+        <v>-0.6632430504792836</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>4971</v>
+        <v>4945</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>IET-KY</t>
+          <t>陞達科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>386.7217050659402</v>
+        <v>499.2651276632713</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>518</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G81" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>32.24811448164407</v>
+        <v>54.06204532545198</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.53955396851394</v>
+        <v>12.95316206891838</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.672170506594017</v>
+        <v>0.4265127663271301</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-24.96165680984078</v>
+        <v>0.5436953806723859</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>5392</v>
+        <v>4972</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>湯石照明</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>382.5597787328118</v>
+        <v>497.5708428923443</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>42.25</v>
+        <v>16.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.86444032595976</v>
+        <v>49.00007477534396</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.73140481645544</v>
+        <v>32.00036273515075</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2559778732811788</v>
+        <v>0.2570842892344294</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3753648281735757</v>
+        <v>0.0363678310376435</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>5452</v>
+        <v>5487</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>佶優</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>379.5611746888001</v>
+        <v>496.8231827111985</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>30.75</v>
+        <v>28.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.5499076700952</v>
+        <v>53.19150842127267</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.357201230741424</v>
+        <v>17.59077019565457</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4561174688800115</v>
+        <v>2.682318271119843</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3615806836559616</v>
+        <v>0.1201681325514899</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>5205</v>
+        <v>4991</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>中茂</t>
+          <t>環宇-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>378.825264344136</v>
+        <v>494.8320335310594</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>23.7</v>
+        <v>530</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.76641639890199</v>
+        <v>35.90449968227638</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.53275053267375</v>
+        <v>22.62788282322008</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8825264344136007</v>
+        <v>1.983203353105944</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1649364071460202</v>
+        <v>-30.81723640665152</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>5489</v>
+        <v>5234</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>彩富</t>
+          <t>達興材料</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>378.4754473684059</v>
+        <v>491.0615155719255</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>39.45</v>
+        <v>381</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.44473567535038</v>
+        <v>39.71272309951955</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>32.73673591330964</v>
+        <v>15.98049299183345</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3475447368405854</v>
+        <v>0.6061515571925487</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0525801609518222</v>
+        <v>-3.945179754027997</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>5220</v>
+        <v>4934</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>萬達光電</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>374.8973111872094</v>
+        <v>483.9730979426221</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>20.9</v>
+        <v>16.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.79893629434347</v>
+        <v>49.07409362409582</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>34.39044337508198</v>
+        <v>12.2719923875534</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4897311187209403</v>
+        <v>0.8973097942622139</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3514815885163687</v>
+        <v>-0.1006752483971843</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6125</v>
+        <v>4971</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>IET-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>374.2998379534064</v>
+        <v>476.7217050659402</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>59.9</v>
+        <v>518</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.64482571226511</v>
+        <v>32.24811447136233</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30.92656478540023</v>
+        <v>15.5395538905193</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.429983795340645</v>
+        <v>1.672170506594017</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.9781928488632692</v>
+        <v>-24.96165680984078</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6124</v>
+        <v>4942</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>業強</t>
+          <t>嘉彰</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>368.3302917371271</v>
+        <v>466.5563606684268</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30.35</v>
+        <v>37.45</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.83989897833361</v>
+        <v>45.17706034471779</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>32.98163303751421</v>
+        <v>20.50915949517448</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.333029173712706</v>
+        <v>0.6556360668426761</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0354388458560145</v>
+        <v>-0.0459594734357301</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>5258</v>
+        <v>6128</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>上福</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>360.9337343918437</v>
+        <v>462.6416036303414</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>50.6</v>
+        <v>20.3</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.74638943048431</v>
+        <v>52.03044706552937</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.50702595639196</v>
+        <v>26.71277293517142</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.593373439184362</v>
+        <v>1.264160363034145</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.6632430503457253</v>
+        <v>0.152734964981905</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>4908</v>
+        <v>5292</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>360.364692797981</v>
+        <v>455.9438171674514</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>192.5</v>
+        <v>209</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.98753477126395</v>
+        <v>40.47844843915104</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>31.77204533854999</v>
+        <v>20.54323999323054</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.036469279798103</v>
+        <v>1.094381716745133</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-9.283220961205611</v>
+        <v>-2.03635115823157</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>4972</v>
+        <v>4974</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>湯石照明</t>
+          <t>亞泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>357.5708428923443</v>
+        <v>455.0791877473145</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>16.6</v>
+        <v>74.8</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.00007489688471</v>
+        <v>47.45231584239041</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>32.00036197481382</v>
+        <v>24.24404824987813</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2570842892344294</v>
+        <v>0.5079187747314444</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0363678310758016</v>
+        <v>-0.389029738351806</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>5203</v>
+        <v>4908</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>訊連</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>356.7721106551435</v>
+        <v>450.364692797981</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>68</v>
+        <v>192.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.46367160459898</v>
+        <v>40.98753476142565</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.69131748133176</v>
+        <v>31.77204533089564</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6772110655143523</v>
+        <v>1.036469279798103</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0527729130869694</v>
+        <v>-9.283220961167409</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>4943</v>
+        <v>5432</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>康控-KY</t>
+          <t>新門</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>356.3423279247535</v>
+        <v>440.7575228919337</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>8.99</v>
+        <v>138.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.70012552304998</v>
+        <v>51.62141692405868</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.66204603936194</v>
+        <v>14.23267369462604</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.634232792475355</v>
+        <v>3.575752289193365</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0560435469513125</v>
+        <v>-0.0896549792750605</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>5236</v>
+        <v>5457</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>凌陽創新</t>
+          <t>宣德</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>353.8931446371147</v>
+        <v>439.8165078442468</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>154.5</v>
+        <v>32.35</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.20639630522681</v>
+        <v>52.36279325752349</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>33.56805062542998</v>
+        <v>18.39293584109336</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3893144637114672</v>
+        <v>1.481650784424673</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-4.037207762417165</v>
+        <v>0.338707446534489</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4933</v>
+        <v>5251</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>天鉞電</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>353.5697186150039</v>
+        <v>438.1189228297058</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>65.8</v>
+        <v>30</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.97870577472742</v>
+        <v>53.0209614885732</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>30.15822212824153</v>
+        <v>32.61791354922757</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3569718615003845</v>
+        <v>0.3118922829705813</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.42263817103388</v>
+        <v>0.2283779401157546</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>4585</v>
+        <v>4554</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>達明</t>
+          <t>橙的</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>351.2882607681116</v>
+        <v>417.5504119036868</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>307</v>
+        <v>29.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>39.41076616754582</v>
+        <v>43.52486674465536</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.23047970617596</v>
+        <v>26.63242984100754</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6288260768111648</v>
+        <v>0.7550411903686753</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-5.361492710592617</v>
+        <v>-0.1228959293107646</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>4934</v>
+        <v>4582</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>聚恆-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>343.9360946874092</v>
+        <v>410.4232275126193</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>16.8</v>
+        <v>25.9</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.07409367354048</v>
+        <v>42.79279587257537</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.27199240298699</v>
+        <v>17.20857172337013</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8936094687409222</v>
+        <v>1.042322751261934</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1006752483971843</v>
+        <v>0.2282104310806645</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>4749</v>
+        <v>4949</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>有成精密</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>342.961059978588</v>
+        <v>409.7486762295982</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>908</v>
+        <v>90</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>37.18669211564939</v>
+        <v>45.25568782418675</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.01615317529283</v>
+        <v>23.57290957349411</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7961059978587968</v>
+        <v>0.4748676229598192</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-23.932731138829</v>
+        <v>-1.54822995155789</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>4974</v>
+        <v>5460</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>亞泰</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>340.0791877473144</v>
+        <v>409.461998777781</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>74.8</v>
+        <v>14.65</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.45231599190802</v>
+        <v>39.55378582912103</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24.24404818202416</v>
+        <v>33.50124130834003</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5079187747314444</v>
+        <v>0.4461998777781011</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.389029738351806</v>
+        <v>-0.0636610360849265</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>5278</v>
+        <v>4729</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>尚凡</t>
+          <t>熒茂</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>338.6270914349769</v>
+        <v>403.2005606842843</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>24.5</v>
+        <v>21.1</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>56.56075521616288</v>
+        <v>39.75969931764176</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.35997888469902</v>
+        <v>38.89966856227921</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.362709143497696</v>
+        <v>0.3200560684284319</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.137638160554659</v>
+        <v>-0.5620633120828956</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5475</v>
+        <v>4951</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>精拓科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>337.950549203357</v>
+        <v>398.7698041159516</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>238</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.47723319390139</v>
+        <v>36.15632891783849</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.9428860498735</v>
+        <v>32.66355336917735</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7950549203357022</v>
+        <v>0.8769804115951607</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-5.886665386162386</v>
+        <v>-4.516781093748968</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>5340</v>
+        <v>5215</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>科嘉-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>337.6490217432245</v>
+        <v>396.0715427748427</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>85.8</v>
+        <v>42.15</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>29.31948287671</v>
+        <v>40.53030428622333</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.25246155262632</v>
+        <v>44.85194136535935</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7649021743224494</v>
+        <v>1.107154277484275</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.559875903999285</v>
+        <v>-0.9070166235335488</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6120</v>
+        <v>6109</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>達運</t>
+          <t>亞元</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>336.7017750364516</v>
+        <v>393.5424843633919</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>13.35</v>
+        <v>11.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.70382311237059</v>
+        <v>46.85945589109464</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.05331168556413</v>
+        <v>15.36445451190201</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6701775036451569</v>
+        <v>0.354248436339193</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1525455232605638</v>
+        <v>0.0432873180233454</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5487</v>
+        <v>6133</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>金橋</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>326.8231827111985</v>
+        <v>392.7778857412566</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>28.1</v>
+        <v>22.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.19150830132136</v>
+        <v>46.74362516487477</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.59077008602685</v>
+        <v>13.27358609543282</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.682318271119843</v>
+        <v>0.2777885741256617</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1201681326087283</v>
+        <v>-0.1012755054731619</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>4942</v>
+        <v>4956</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>嘉彰</t>
+          <t>光鋐</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>326.5155094036048</v>
+        <v>384.4378115523163</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>37.45</v>
+        <v>37.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.17706045845005</v>
+        <v>35.13087146506196</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>20.50915941974106</v>
+        <v>19.88679820785196</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6515509403604763</v>
+        <v>0.443781155231633</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0459594734357301</v>
+        <v>-1.110429042729478</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>5371</v>
+        <v>5392</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>能率</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>321.6079133603835</v>
+        <v>382.5597787328118</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>67.7</v>
+        <v>42.25</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.21499426559349</v>
+        <v>47.86444027235862</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.70159734373432</v>
+        <v>12.73140482670696</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6607913360383458</v>
+        <v>0.2559778732811788</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.3834898385686153</v>
+        <v>-0.3753648282021919</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>5348</v>
+        <v>5225</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>320.6138230170299</v>
+        <v>380.4706596795604</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16.45</v>
+        <v>71.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>53.65872910491491</v>
+        <v>43.55704292617479</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.59667928966532</v>
+        <v>32.77278246495763</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5613823017029901</v>
+        <v>0.5470659679560362</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.3909080993569584</v>
+        <v>0.2723474645334383</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>5344</v>
+        <v>5452</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>立衛</t>
+          <t>佶優</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>318.5149210287112</v>
+        <v>379.5611746888001</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15.4</v>
+        <v>30.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.34164930676372</v>
+        <v>40.54990763145362</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.36827198707414</v>
+        <v>9.3572013612017</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3514921028711177</v>
+        <v>0.4561174688800115</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0755890747231089</v>
+        <v>-0.3615806834747072</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6128</v>
+        <v>5220</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>上福</t>
+          <t>萬達光電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>317.6255612061956</v>
+        <v>374.8973111872094</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.03044712653791</v>
+        <v>38.79893626695701</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>26.71277290018683</v>
+        <v>34.39044338709417</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.262556120619562</v>
+        <v>0.4897311187209403</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1527349650200671</v>
+        <v>-0.3514815885068259</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>5225</v>
+        <v>6125</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>310.3719939135701</v>
+        <v>374.2998379534064</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>71.3</v>
+        <v>59.9</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.55704314776533</v>
+        <v>44.64482561012285</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>32.77278245362742</v>
+        <v>30.92656481475906</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5371993913570108</v>
+        <v>0.429983795340645</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2723474643998888</v>
+        <v>-0.9781928488060304</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6133</v>
+        <v>6124</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>金橋</t>
+          <t>業強</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>302.7673091297362</v>
+        <v>368.3302917371271</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>22.75</v>
+        <v>30.35</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.74362525648204</v>
+        <v>46.83989896880387</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.27358606665351</v>
+        <v>32.98163303175109</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2767309129736263</v>
+        <v>0.333029173712706</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1012755055208616</v>
+        <v>0.0354388458655538</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>4927</v>
+        <v>5203</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>泰鼎-KY</t>
+          <t>訊連</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>301.0311506954459</v>
+        <v>356.8602232118554</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>48.8</v>
+        <v>68</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.73520280105096</v>
+        <v>53.46367142596962</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.99607073357411</v>
+        <v>20.69131749264501</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.603115069544597</v>
+        <v>0.6860223211855438</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.8323081417518509</v>
+        <v>0.0527729129724794</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>4960</v>
+        <v>5236</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>凌陽創新</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>296.2307754336549</v>
+        <v>353.8931446371147</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>28.95</v>
+        <v>154.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.01301163390681</v>
+        <v>40.20639627895604</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.44119551196338</v>
+        <v>33.56805062542999</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.623077543365492</v>
+        <v>0.3893144637114672</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.6371686454887886</v>
+        <v>-4.037207762607954</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>4935</v>
+        <v>4933</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>茂林-KY</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>295.5364236591554</v>
+        <v>353.5697186150039</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>37.75</v>
+        <v>65.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.53174419867345</v>
+        <v>36.97870571198485</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.55018153726368</v>
+        <v>30.15822214566651</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5536423659155443</v>
+        <v>0.3569718615003845</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2052901770417122</v>
+        <v>-1.422638171014808</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>5292</v>
+        <v>4585</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>達明</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>295.5054519673141</v>
+        <v>351.800019609274</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.47844847425837</v>
+        <v>39.41076622694673</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.54323997700037</v>
+        <v>20.2304797781072</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.050545196731407</v>
+        <v>0.6800019609273954</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.036351158327014</v>
+        <v>-5.36149271335912</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>5460</v>
+        <v>5315</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>光聯</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>294.461998777781</v>
+        <v>350.4400178915616</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.65</v>
+        <v>22.05</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>39.55378580510642</v>
+        <v>45.32271840906924</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>33.50124133423587</v>
+        <v>13.78206662698591</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4461998777781011</v>
+        <v>0.5440017891561579</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0636610360849265</v>
+        <v>0.0198641244278453</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>5222</v>
+        <v>5287</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>全訊</t>
+          <t>數字</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>283.2971417973399</v>
+        <v>349.8943192001451</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>112.5</v>
+        <v>146.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>30.38387310760734</v>
+        <v>39.87676382221162</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>20.20918298077339</v>
+        <v>20.01569725389425</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.8297141797339872</v>
+        <v>0.4894319200145113</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.071562875081545</v>
+        <v>0.2925236268668039</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6109</v>
+        <v>4994</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>亞元</t>
+          <t>傳奇</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>278.542484363392</v>
+        <v>343.4715048602163</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.2</v>
+        <v>87.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.85945596181993</v>
+        <v>41.74778200146735</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.36445481893676</v>
+        <v>19.65045318279774</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.354248436339193</v>
+        <v>0.3471504860216309</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0432873179508425</v>
+        <v>-0.0678176817482589</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4554</v>
+        <v>4749</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>橙的</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>277.5504119036867</v>
+        <v>342.961059978588</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>29.8</v>
+        <v>908</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.52486694074607</v>
+        <v>37.18669209167305</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>26.6324298508736</v>
+        <v>20.01615318449141</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7550411903686753</v>
+        <v>0.7961059978587968</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1228959293870839</v>
+        <v>-23.93273114035543</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6103</v>
+        <v>4909</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>合邦</t>
+          <t>新復興</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>275.8954555630177</v>
+        <v>340.2031236026493</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.48656891825832</v>
+        <v>36.40109407675766</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9.69376129864359</v>
+        <v>29.43120700170385</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.0895455563017685</v>
+        <v>0.5203123602649246</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.998978977175542</v>
+        <v>-0.389335202614163</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>5457</v>
+        <v>5475</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>宣德</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>269.8165078442468</v>
+        <v>337.950549203357</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>32.35</v>
+        <v>238</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.36279330001234</v>
+        <v>36.4772331936498</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.39293580799333</v>
+        <v>18.94288606995555</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.481650784424673</v>
+        <v>0.7950549203357022</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.3387074465154125</v>
+        <v>-5.886665386200527</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6136</v>
+        <v>5340</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>269.2525902514932</v>
+        <v>337.6490217432245</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>25</v>
+        <v>85.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>43.81412644796991</v>
+        <v>29.31948286714652</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.29741845766384</v>
+        <v>15.25246159190055</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.9252590251493208</v>
+        <v>0.7649021743224494</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1115404552452049</v>
+        <v>-1.559875903980206</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>5443</v>
+        <v>6120</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>均豪</t>
+          <t>達運</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>265.6567739096643</v>
+        <v>336.7286076739452</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>100.5</v>
+        <v>13.35</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,49 +6965,49 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>32.90927480730755</v>
+        <v>43.70382307956537</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.93683776503273</v>
+        <v>18.05331169889556</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5656773909664332</v>
+        <v>0.6728607673945203</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-3.145499358918016</v>
+        <v>-0.1525455232605638</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5439</v>
+        <v>4903</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>260.3287549842755</v>
+        <v>329.2462589491579</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>346</v>
+        <v>38.55</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.97550458775967</v>
+        <v>32.86484113681669</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.84953454843353</v>
+        <v>15.19781505251072</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.032875498427549</v>
+        <v>0.4246258949157965</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-4.320683298015497</v>
+        <v>-0.7415320511296146</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4977</v>
+        <v>5223</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>眾達-KY</t>
+          <t>安力-KY</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>257.1558354183645</v>
+        <v>323.6477414537688</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>173.5</v>
+        <v>25.1</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>42.37357695972215</v>
+        <v>47.17675993877111</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.9208255469847</v>
+        <v>16.46891453620189</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7155835418364438</v>
+        <v>0.3647741453768763</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-5.295570115103216</v>
+        <v>0.0457118512494975</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>5272</v>
+        <v>5371</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>笙科</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>254.5568325385608</v>
+        <v>321.6079133603835</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>20.35</v>
+        <v>67.7</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>34.78670637769035</v>
+        <v>38.21499419003239</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.95677078583922</v>
+        <v>13.70159730874551</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9556832538560824</v>
+        <v>0.6607913360383458</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.2524943329861774</v>
+        <v>-0.3834898385304438</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4903</v>
+        <v>5344</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>254.246258949158</v>
+        <v>318.5149210287112</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>38.55</v>
+        <v>15.4</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>32.86484115831662</v>
+        <v>44.34164927580185</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>15.1978150256299</v>
+        <v>19.36827200493381</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4246258949157965</v>
+        <v>0.3514921028711177</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.7415320510628364</v>
+        <v>-0.0755890747326495</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>5291</v>
+        <v>6152</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>邑昇</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>253.8618514521877</v>
+        <v>311.5545360831283</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>64.2</v>
+        <v>14.7</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.48115252929531</v>
+        <v>44.7201161889129</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>19.05778945334404</v>
+        <v>10.44318366968996</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.3861851452187674</v>
+        <v>0.6554536083128333</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-1.041275753034755</v>
+        <v>-0.031950388780855</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>5469</v>
+        <v>4927</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>泰鼎-KY</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>246.7373535957838</v>
+        <v>306.0794292332727</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>42.92047777498933</v>
+        <v>42.73520276335099</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>16.72874767012526</v>
+        <v>20.99607071052688</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.6737353595783798</v>
+        <v>0.6079429233272721</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.2448488157497066</v>
+        <v>-0.8323081418090856</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>5432</v>
+        <v>4960</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>新門</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>240.7575228919337</v>
+        <v>296.2709508060323</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>138.5</v>
+        <v>28.95</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>51.62141719861986</v>
+        <v>38.01301162566952</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>14.23267366454958</v>
+        <v>17.44119550810721</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>3.575752289193365</v>
+        <v>0.6270950806032297</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.0896549816599812</v>
+        <v>-0.6371686454792516</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>5465</v>
+        <v>4935</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>富驊</t>
+          <t>茂林-KY</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>236.9955677547094</v>
+        <v>295.5697601744919</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>25.6</v>
+        <v>37.75</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.06092329140855</v>
+        <v>46.53174414764682</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>27.48593524116538</v>
+        <v>20.5501815450261</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.6995567754709446</v>
+        <v>0.5569760174491889</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.06362692933407289</v>
+        <v>-0.2052901770703323</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>6117</v>
+        <v>4588</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>迎廣</t>
+          <t>玖鼎電力</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>235.8828398091392</v>
+        <v>289.1749253540065</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>57</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>38.34835441930754</v>
+        <v>46.81128236192561</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>17.56901043683326</v>
+        <v>20.85578376877917</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.588283980913923</v>
+        <v>0.4174925354006492</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-1.302612023925911</v>
+        <v>0.1382399425618556</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>5234</v>
+        <v>4977</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>達興材料</t>
+          <t>眾達-KY</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>235.7466692311849</v>
+        <v>277.3073082344883</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>381</v>
+        <v>173.5</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>39.71272311813796</v>
+        <v>42.37357694162444</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>15.98049299784815</v>
+        <v>11.92082554247714</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.5746669231184945</v>
+        <v>0.7307308234488303</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-3.945179753741765</v>
+        <v>-5.29557011485517</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>4582</v>
+        <v>6103</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>聚恆-創</t>
+          <t>合邦</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>230.3732248840209</v>
+        <v>275.8954555630177</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>42.79279590314053</v>
+        <v>44.48656892129008</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17.20857167480479</v>
+        <v>9.693761221187923</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.037322488402087</v>
+        <v>0.0895455563017685</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.2282104311092827</v>
+        <v>-1.998978977166003</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>4905</v>
+        <v>6129</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>台聯電</t>
+          <t>普誠</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>227.2103734102325</v>
+        <v>266.782904609948</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>15</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>39.02149622795709</v>
+        <v>42.00514356975487</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>12.83393715083452</v>
+        <v>13.31100559799883</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.7210373410232523</v>
+        <v>0.6782904609948058</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.913193597545486</v>
+        <v>-0.1023182481929947</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7629,21 +7629,21 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>4909</v>
+        <v>5443</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>新復興</t>
+          <t>均豪</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>225.2031236026492</v>
+        <v>265.6567739096643</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>48.1</v>
+        <v>100.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>36.40109418222112</v>
+        <v>32.90927477517209</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>29.43120705704809</v>
+        <v>18.93683772159203</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.5203123602649246</v>
+        <v>0.5656773909664332</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.3893352023852079</v>
+        <v>-3.145499358841698</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>4999</v>
+        <v>5439</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>鑫禾</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>220.8587622514278</v>
+        <v>260.3287549842755</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>20.3</v>
+        <v>346</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>44.91938432064657</v>
+        <v>39.97550454038578</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>20.43709043091419</v>
+        <v>18.84953454721266</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.5858762251427837</v>
+        <v>1.032875498427549</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.0590892709258019</v>
+        <v>-4.320683298301694</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5438</v>
+        <v>5272</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>東友</t>
+          <t>笙科</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>219.5642987839968</v>
+        <v>254.5568325385608</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>18.65</v>
+        <v>20.35</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>41.38494194690004</v>
+        <v>34.78670630541637</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>22.01154849824442</v>
+        <v>15.95677080074566</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.4564298783996768</v>
+        <v>0.9556832538560824</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.0363854278292615</v>
+        <v>-0.2524943329575597</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>4588</v>
+        <v>5469</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>玖鼎電力</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>219.1349250865285</v>
+        <v>246.8121705057071</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>57</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>46.81128235496344</v>
+        <v>42.92047773822151</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>20.85578372059892</v>
+        <v>16.72874767461079</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.4134925086528476</v>
+        <v>0.6812170505707086</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.1382399428289666</v>
+        <v>-0.2448488157687899</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>5315</v>
+        <v>5465</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>光聯</t>
+          <t>富驊</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>210.4400178915616</v>
+        <v>236.9955677547094</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>22.05</v>
+        <v>25.6</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>45.32271851158929</v>
+        <v>46.06092312222707</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>13.78206659698354</v>
+        <v>27.48593530028096</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5440017891561579</v>
+        <v>0.6995567754709446</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.0198641244087679</v>
+        <v>-0.06362692933407289</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>6114</v>
+        <v>4905</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>久威</t>
+          <t>台聯電</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>209.5821958533447</v>
+        <v>227.2103734102325</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>29.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>42.63953723027539</v>
+        <v>39.02149606118778</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>36.55363967487445</v>
+        <v>12.83393723032058</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.4582195853344697</v>
+        <v>0.7210373410232523</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.1456962376272866</v>
+        <v>-0.9131935968204764</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>5223</v>
+        <v>4999</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>安力-KY</t>
+          <t>鑫禾</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>208.6477414537688</v>
+        <v>221.0462565151185</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>25.1</v>
+        <v>20.3</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>47.17675998226264</v>
+        <v>44.91938424865544</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>16.46891462422834</v>
+        <v>20.43709055446907</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.3647741453768763</v>
+        <v>0.6046256515118474</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.0457118512494975</v>
+        <v>0.0590892709353404</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>6152</v>
+        <v>5438</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>東友</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>196.5429789111714</v>
+        <v>219.5642987839968</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>14.7</v>
+        <v>18.65</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>44.72011623987557</v>
+        <v>41.38494183436539</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>10.44318369336804</v>
+        <v>22.01154850689765</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.6542978911171398</v>
+        <v>0.4564298783996768</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.0319503888132877</v>
+        <v>-0.0363854278197282</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>6108</v>
+        <v>6117</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>競國</t>
+          <t>迎廣</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>195.6553241607377</v>
+        <v>215.9766653212117</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>18.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>41.05101539072272</v>
+        <v>38.34835432526115</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>17.18258309380737</v>
+        <v>17.56901047646839</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.5655324160737678</v>
+        <v>0.5976665321211785</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.2206057355983074</v>
+        <v>-1.30261202362063</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>5314</v>
+        <v>5222</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>世紀*</t>
+          <t>全訊</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>194.7404655682871</v>
+        <v>213.6071741712698</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>58.4</v>
+        <v>112.5</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>44.10826919619064</v>
+        <v>30.38387307408179</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>6.617473733865285</v>
+        <v>20.20918298077339</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.474046556828711</v>
+        <v>0.8607174171269835</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.0480730083340907</v>
+        <v>-1.071562875176944</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>4994</v>
+        <v>6114</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>傳奇</t>
+          <t>久威</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>193.2882267780401</v>
+        <v>209.5821958533447</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>87.5</v>
+        <v>29.2</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>41.74778193038444</v>
+        <v>42.63953740875033</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>19.65045318105069</v>
+        <v>36.55363969235702</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.3288226778040125</v>
+        <v>0.4582195853344697</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.0678176816337758</v>
+        <v>-0.145696237331554</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>5287</v>
+        <v>5244</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>數字</t>
+          <t>弘凱</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>179.8943192001451</v>
+        <v>202.906956114831</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>146.5</v>
+        <v>36.8</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>39.87676401430992</v>
+        <v>39.87926271402627</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>20.0156972655664</v>
+        <v>13.71715518754623</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.4894319200145113</v>
+        <v>0.2906956114831044</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.2925236266760236</v>
+        <v>-0.1844999729368993</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>5244</v>
+        <v>6108</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>弘凱</t>
+          <t>競國</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>162.8913941797246</v>
+        <v>199.3806643150644</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>36.8</v>
+        <v>18.25</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>39.87926284806758</v>
+        <v>41.05101537579717</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>13.71715520199239</v>
+        <v>17.18258310572273</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.2891394179724614</v>
+        <v>0.9380664315064424</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.1844999731086114</v>
+        <v>-0.2206057355983074</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>4968</v>
+        <v>6136</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>立積</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>154.9880746443893</v>
+        <v>199.3299808716237</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>35.2475945683513</v>
+        <v>43.81412647843962</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>17.22854989226816</v>
+        <v>12.2974184612986</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.4988074644389288</v>
+        <v>0.9329980871623702</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>0</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-1.490088983175029</v>
+        <v>-0.1115404552547424</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>6118</v>
+        <v>5314</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>建達</t>
+          <t>世紀*</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>148.5545143118157</v>
+        <v>194.7404655682871</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>16.7</v>
+        <v>58.4</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>40.90722747505308</v>
+        <v>44.10826916560084</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>24.70267236563041</v>
+        <v>6.617473859633422</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.3554514311815703</v>
+        <v>0.474046556828711</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,11 +8414,11 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.1643561270585767</v>
+        <v>-0.048073008925543</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>134.0096999358743</v>
+        <v>184.0395119404556</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>8.279999999999999</v>
@@ -8449,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>43.57015447680963</v>
+        <v>43.57015443350506</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>19.38731181095193</v>
+        <v>19.38731179412622</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.4009699935874284</v>
+        <v>0.403951194045558</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>0</v>
@@ -8467,11 +8467,117 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.0309801404912976</v>
+        <v>0.030980140489391</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>4968</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>立積</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>175.1025643451831</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>35.24759445399931</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>17.22854986277012</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.5102564345183087</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>-1.490088983270424</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>6118</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>建達</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>148.5545143118157</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>40.90722742995175</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>24.70267238553046</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.3554514311815703</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>-0.1643561270490344</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
